--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484057_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484057_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6755</v>
+        <v>6.8195</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5862</v>
+        <v>5.9546</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0893</v>
+        <v>0.8649</v>
       </c>
       <c r="G2" t="n">
         <v>5.941</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.059</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7368</v>
+        <v>-0.3684</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6778</v>
+        <v>0.4534</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9964</v>
+        <v>5.265</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4113</v>
+        <v>3.9161</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5851</v>
+        <v>1.3489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4936</v>
+        <v>4.7709</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8797</v>
+        <v>-0.3633</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3861</v>
+        <v>5.1342</v>
       </c>
       <c r="J3" t="n">
-        <v>1.789</v>
+        <v>5.1464</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8682</v>
+        <v>0.1613</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0793</v>
+        <v>4.9851</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2953</v>
+        <v>-0.3756</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9885</v>
+        <v>-0.5246</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6932</v>
+        <v>0.149</v>
       </c>
       <c r="P3" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.7855</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.9838</v>
-      </c>
       <c r="S3" t="n">
-        <v>-0.0924</v>
+        <v>-0.5654</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.255</v>
+        <v>-0.5044</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1626</v>
+        <v>-0.061</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0757</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7064</v>
+        <v>4.9683</v>
       </c>
       <c r="E4" t="n">
-        <v>3.61</v>
+        <v>3.4113</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0964</v>
+        <v>1.557</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7709</v>
+        <v>1.4936</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3633</v>
+        <v>1.8797</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1342</v>
+        <v>-0.3861</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1464</v>
+        <v>1.789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1613</v>
+        <v>2.8682</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9851</v>
+        <v>-1.0793</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3756</v>
+        <v>-0.2953</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5246</v>
+        <v>-0.9885</v>
       </c>
       <c r="O4" t="n">
-        <v>0.149</v>
+        <v>0.6932</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.124</v>
+        <v>-0.1205</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8105</v>
+        <v>-0.255</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3135</v>
+        <v>0.1345</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>2.0757</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1676</v>
+        <v>3.5656</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5184</v>
+        <v>3.0286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6492</v>
+        <v>0.537</v>
       </c>
       <c r="G5" t="n">
         <v>2.67</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2959</v>
+        <v>0.102</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8105</v>
+        <v>-0.3003</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4024</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8089</v>
+        <v>3.2958</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7657</v>
+        <v>1.1965</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0432</v>
+        <v>2.0993</v>
       </c>
       <c r="G6" t="n">
         <v>2.261</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4954</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>-0.6177</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5531</v>
+        <v>0.6092</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9405</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9961</v>
+        <v>2.2906</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1822</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1783</v>
+        <v>3.2064</v>
       </c>
       <c r="G7" t="n">
         <v>0.6062</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0663</v>
+        <v>0.2281</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8728</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8065</v>
+        <v>0.8345</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. PARADEDA VIDAL</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5407</v>
+        <v>0.6421</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1622</v>
+        <v>-1.7695</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6214</v>
+        <v>2.4117</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1735</v>
+        <v>1.5452</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2975</v>
+        <v>0.5386</v>
       </c>
       <c r="I8" t="n">
-        <v>1.876</v>
+        <v>1.0066</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4851</v>
+        <v>1.439</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1598</v>
+        <v>1.3911</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3253</v>
+        <v>0.0478</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3116</v>
+        <v>0.1063</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8623</v>
+        <v>-0.8525</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5507</v>
+        <v>0.9588</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4466</v>
+        <v>0.2196</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5418</v>
+        <v>-0.3003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0953</v>
+        <v>0.5199</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.881</v>
+        <v>0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>E. PARADEDA VIDAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9875</v>
+        <v>0.4286</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.543</v>
+        <v>0.9378</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5305</v>
+        <v>-0.5092</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4239</v>
+        <v>2.1735</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2347</v>
+        <v>0.2975</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8109</v>
+        <v>1.876</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4775</v>
+        <v>2.4851</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6494</v>
+        <v>1.1598</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8280999999999999</v>
+        <v>1.3253</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0537</v>
+        <v>-0.3116</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5853</v>
+        <v>-0.8623</v>
       </c>
       <c r="O9" t="n">
-        <v>1.639</v>
+        <v>0.5507</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8082</v>
+        <v>0.3344</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1168</v>
+        <v>0.3175</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6914</v>
+        <v>0.017</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3221</v>
+        <v>0.3492</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.342</v>
+        <v>0.4829</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6642</v>
+        <v>-0.1336</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5452</v>
+        <v>0.1761</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5386</v>
+        <v>0.2267</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0066</v>
+        <v>-0.0506</v>
       </c>
       <c r="J10" t="n">
-        <v>1.439</v>
+        <v>0.6812</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3911</v>
+        <v>0.7513</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0478</v>
+        <v>-0.0701</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1063</v>
+        <v>-0.5051</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8525</v>
+        <v>-0.5246</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9588</v>
+        <v>0.0195</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1004</v>
+        <v>0.1261</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8728</v>
+        <v>-0.1983</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7724</v>
+        <v>0.3244</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>-1.7384</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1262</v>
+        <v>0.0919</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6246</v>
+        <v>-3.4386</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4984</v>
+        <v>3.5305</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1761</v>
+        <v>-0.4239</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2267</v>
+        <v>-1.2347</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0506</v>
+        <v>0.8109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6812</v>
+        <v>-1.4775</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7513</v>
+        <v>-0.6494</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0701</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5051</v>
+        <v>1.0537</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5246</v>
+        <v>-0.5853</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0195</v>
+        <v>1.639</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7855</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R11" t="n">
         <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0969</v>
+        <v>0.9126</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0566</v>
+        <v>0.2212</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0403</v>
+        <v>0.6914</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1827</v>
+        <v>-0.9483</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.694</v>
+        <v>-2.2632</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5113</v>
+        <v>1.3149</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4607</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.301</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7368</v>
+        <v>-0.306</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4358</v>
+        <v>0.2394</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.1447</v>
+        <v>26.7683</v>
       </c>
       <c r="E13" t="n">
-        <v>9.917200000000001</v>
+        <v>10.5407</v>
       </c>
       <c r="F13" t="n">
-        <v>16.2277</v>
+        <v>16.2278</v>
       </c>
       <c r="G13" t="n">
         <v>19.7529</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0731</v>
+        <v>3.073100000000001</v>
       </c>
       <c r="I13" t="n">
         <v>16.6798</v>
@@ -1444,13 +1444,13 @@
         <v>19.7064</v>
       </c>
       <c r="K13" t="n">
-        <v>9.958600000000001</v>
+        <v>9.958599999999999</v>
       </c>
       <c r="L13" t="n">
         <v>9.7477</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0464</v>
+        <v>0.04640000000000039</v>
       </c>
       <c r="N13" t="n">
         <v>-6.8855</v>
@@ -1468,10 +1468,10 @@
         <v>18.8466</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6235000000000002</v>
+        <v>1.2468</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.541700000000001</v>
+        <v>-2.9181</v>
       </c>
       <c r="U13" t="n">
         <v>4.1651</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8304</v>
+        <v>4.0709</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5977</v>
+        <v>5.3936</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7673</v>
+        <v>-1.3227</v>
       </c>
       <c r="G14" t="n">
         <v>2.3793</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3667</v>
+        <v>-0.1261</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1699</v>
+        <v>-0.374</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1968</v>
+        <v>0.2479</v>
       </c>
       <c r="V14" t="n">
         <v>2.4129</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2713</v>
+        <v>-0.375</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1869</v>
+        <v>-1.595</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9156</v>
+        <v>1.22</v>
       </c>
       <c r="G15" t="n">
         <v>0.5338000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6394</v>
+        <v>0.5357</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4252</v>
+        <v>0.0171</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2142</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.1425</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7389</v>
+        <v>-1.6871</v>
       </c>
       <c r="E16" t="n">
         <v>-1.981</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2421</v>
+        <v>0.2939</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6091</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="T16" t="n">
         <v>-0.544</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6126</v>
+        <v>0.6645</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.4557</v>
+        <v>-3.3605</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6133</v>
+        <v>-1.2052</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8424</v>
+        <v>-2.1553</v>
       </c>
       <c r="G17" t="n">
         <v>-3.8916</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2051</v>
+        <v>0.3004</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.3797</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9929</v>
+        <v>0.68</v>
       </c>
       <c r="V17" t="n">
         <v>2.4129</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7243</v>
+        <v>-3.3723</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2234</v>
+        <v>-2.8153</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5008</v>
+        <v>-0.5569</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0274</v>
@@ -1858,13 +1858,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6212</v>
+        <v>-0.2692</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3092</v>
+        <v>-0.9011</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6319</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8218</v>
+        <v>-3.7139</v>
       </c>
       <c r="E19" t="n">
         <v>-3.0826</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7392</v>
+        <v>-0.6312</v>
       </c>
       <c r="G19" t="n">
         <v>-3.2481</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1683</v>
+        <v>0.2763</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1926</v>
       </c>
       <c r="U19" t="n">
-        <v>0.361</v>
+        <v>0.469</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9405</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0928</v>
+        <v>-4.8581</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9717</v>
+        <v>-3.0737</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1211</v>
+        <v>-1.7844</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4095</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.501</v>
+        <v>-0.2664</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6914</v>
+        <v>-0.7934</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1904</v>
+        <v>0.5271</v>
       </c>
       <c r="V20" t="n">
         <v>1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3716</v>
+        <v>-5.8461</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5194</v>
+        <v>-4.8255</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8522</v>
+        <v>-1.0205</v>
       </c>
       <c r="G21" t="n">
         <v>-4.2594</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4829</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1418</v>
+        <v>-0.1643</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3411</v>
+        <v>0.1728</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6032</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4988</v>
+        <v>-6.3228</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2471</v>
+        <v>-3.043</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2517</v>
+        <v>-3.2798</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2209</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6989</v>
+        <v>-0.5229</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0372</v>
+        <v>-0.8331</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3383</v>
+        <v>0.3102</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-26.1448</v>
+        <v>-25.4649</v>
       </c>
       <c r="E23" t="n">
         <v>-16.2277</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.917</v>
+        <v>-9.236899999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-19.7529</v>
@@ -2248,13 +2248,13 @@
         <v>9.9193</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6234999999999999</v>
+        <v>0.05679999999999996</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.165099999999999</v>
+        <v>-4.1651</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5417</v>
+        <v>4.222</v>
       </c>
       <c r="V23" t="n">
         <v>3.1586</v>
